--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Wavelet Trans/Wavelet+50T+50EP+optim_purn/params_vs_psnr_analysis/WaveletAttention_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Wavelet Trans/Wavelet+50T+50EP+optim_purn/params_vs_psnr_analysis/WaveletAttention_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>2597811</v>
       </c>
       <c r="C2" t="n">
+        <v>1.453996236</v>
+      </c>
+      <c r="D2" t="n">
         <v>27.72437057495117</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>2188373</v>
       </c>
       <c r="C3" t="n">
+        <v>1.300936896</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.04874801635742</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>2193945</v>
       </c>
       <c r="C4" t="n">
+        <v>1.702803648</v>
+      </c>
+      <c r="D4" t="n">
         <v>27.9411247253418</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>1785721</v>
       </c>
       <c r="C5" t="n">
+        <v>0.615009024</v>
+      </c>
+      <c r="D5" t="n">
         <v>29.06948204040527</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>3972889</v>
       </c>
       <c r="C6" t="n">
+        <v>1.265547456</v>
+      </c>
+      <c r="D6" t="n">
         <v>30.18602485656738</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>3401393</v>
       </c>
       <c r="C7" t="n">
+        <v>2.56585182</v>
+      </c>
+      <c r="D7" t="n">
         <v>28.21548881530762</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>1530681</v>
       </c>
       <c r="C8" t="n">
+        <v>0.92643768</v>
+      </c>
+      <c r="D8" t="n">
         <v>27.87568359375</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>1789953</v>
       </c>
       <c r="C9" t="n">
+        <v>0.615009024</v>
+      </c>
+      <c r="D9" t="n">
         <v>27.89075546264649</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>5454305</v>
       </c>
       <c r="C10" t="n">
+        <v>2.191961088</v>
+      </c>
+      <c r="D10" t="n">
         <v>30.22168846130371</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>1530049</v>
       </c>
       <c r="C11" t="n">
+        <v>0.89694648</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.59076194763184</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>5454305</v>
       </c>
       <c r="C12" t="n">
+        <v>2.191961088</v>
+      </c>
+      <c r="D12" t="n">
         <v>29.46869506835937</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>5405009</v>
       </c>
       <c r="C13" t="n">
+        <v>1.697218992</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.30442962646485</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>4188225</v>
       </c>
       <c r="C14" t="n">
+        <v>1.697218992</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.06216659545898</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>5405009</v>
       </c>
       <c r="C15" t="n">
+        <v>1.697218992</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.09422225952148</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>4188225</v>
       </c>
       <c r="C16" t="n">
+        <v>1.697218992</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.02591896057129</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>5454305</v>
       </c>
       <c r="C17" t="n">
+        <v>2.191961088</v>
+      </c>
+      <c r="D17" t="n">
         <v>29.6357738494873</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>4655589</v>
       </c>
       <c r="C18" t="n">
+        <v>1.473499404</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.2387939453125</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>4655589</v>
       </c>
       <c r="C19" t="n">
+        <v>1.473499404</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.25742835998535</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>4655589</v>
       </c>
       <c r="C20" t="n">
+        <v>1.473499404</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.23525886535645</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>3344309</v>
       </c>
       <c r="C21" t="n">
+        <v>1.073363148</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.18966827392578</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>4661477</v>
       </c>
       <c r="C22" t="n">
+        <v>1.971048716</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.25093002319336</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>5398297</v>
       </c>
       <c r="C23" t="n">
+        <v>2.25873144</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.36763763427734</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>5398297</v>
       </c>
       <c r="C24" t="n">
+        <v>2.25873144</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.14602508544922</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>4661477</v>
       </c>
       <c r="C25" t="n">
+        <v>1.971048716</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.25595321655273</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>3978777</v>
       </c>
       <c r="C26" t="n">
+        <v>1.702803648</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.1612174987793</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>4661477</v>
       </c>
       <c r="C27" t="n">
+        <v>1.971048716</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.27004051208496</v>
       </c>
     </row>
@@ -739,6 +822,9 @@
         <v>5398297</v>
       </c>
       <c r="C28" t="n">
+        <v>2.25873144</v>
+      </c>
+      <c r="D28" t="n">
         <v>30.33560256958008</v>
       </c>
     </row>
@@ -750,6 +836,9 @@
         <v>2968085</v>
       </c>
       <c r="C29" t="n">
+        <v>2.25873144</v>
+      </c>
+      <c r="D29" t="n">
         <v>30.28653984069824</v>
       </c>
     </row>
